--- a/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
+++ b/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
@@ -1,39 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ai-project\eda\ket_qua\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C92415-91BA-4BD5-876A-D9F413611EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KFold" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Validation Accuracy</t>
+  </si>
+  <si>
+    <t>Test Accuracy</t>
+  </si>
+  <si>
+    <t>Mean KFold Accuracy</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>F1-score</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,93 +81,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,149 +405,143 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Validation Accuracy</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Test Accuracy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mean KFold Accuracy</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.7248908296943232</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.6802935010482181</v>
+      <c r="B2">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C2">
+        <v>0.72638015373864429</v>
+      </c>
+      <c r="D2">
+        <v>46</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>35</v>
+      </c>
+      <c r="G2">
+        <v>120</v>
+      </c>
+      <c r="H2">
+        <v>0.5859872611464968</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3">
+        <v>0.72489082969432317</v>
+      </c>
+      <c r="C3">
+        <v>0.68029350104821806</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>34</v>
+      </c>
+      <c r="F3">
+        <v>29</v>
+      </c>
+      <c r="G3">
+        <v>116</v>
+      </c>
+      <c r="H3">
+        <v>0.61349693251533743</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C4">
+        <v>0.72638015373864429</v>
+      </c>
+      <c r="D4">
+        <v>46</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <v>35</v>
+      </c>
+      <c r="G4">
+        <v>120</v>
+      </c>
+      <c r="H4">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0.72489082969432317</v>
+      </c>
+      <c r="C5">
+        <v>0.68029350104821806</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>29</v>
+      </c>
+      <c r="G5">
         <v>116</v>
       </c>
-      <c r="B2" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B3" t="n">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KFold Scores</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.6981132075471698</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.6981132075471698</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.6981132075471698</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.6792452830188679</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.6415094339622641</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.5471698113207547</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.6792452830188679</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.7169811320754716</v>
+      <c r="H5">
+        <v>0.61349693251533743</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
+++ b/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
@@ -1,72 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ai-project\eda\ket_qua\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C92415-91BA-4BD5-876A-D9F413611EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Validation Accuracy</t>
-  </si>
-  <si>
-    <t>Test Accuracy</t>
-  </si>
-  <si>
-    <t>Mean KFold Accuracy</t>
-  </si>
-  <si>
-    <t>TP</t>
-  </si>
-  <si>
-    <t>FP</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>F1-score</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -81,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -405,143 +420,366 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Validation Accuracy</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mean KFold Accuracy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.7186147186147186</v>
       </c>
-      <c r="C2">
-        <v>0.72638015373864429</v>
-      </c>
-      <c r="D2">
+      <c r="C2" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D2" t="n">
         <v>46</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>30</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>35</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>120</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.5859872611464968</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>0.72489082969432317</v>
-      </c>
-      <c r="C3">
-        <v>0.68029350104821806</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D3" t="n">
         <v>50</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>34</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>29</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>116</v>
       </c>
-      <c r="H3">
-        <v>0.61349693251533743</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
+      <c r="H3" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
         <v>0.7186147186147186</v>
       </c>
-      <c r="C4">
-        <v>0.72638015373864429</v>
-      </c>
-      <c r="D4">
+      <c r="C4" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D4" t="n">
         <v>46</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>30</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>35</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>0.5859872611464968</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>0.72489082969432317</v>
-      </c>
-      <c r="C5">
-        <v>0.68029350104821806</v>
-      </c>
-      <c r="D5">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D5" t="n">
         <v>50</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>34</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>29</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>116</v>
       </c>
-      <c r="H5">
-        <v>0.61349693251533743</v>
+      <c r="H5" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G7" t="n">
+        <v>116</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D8" t="n">
+        <v>46</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F9" t="n">
+        <v>29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>116</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7117903930131004</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7032844164919636</v>
+      </c>
+      <c r="D10" t="n">
+        <v>68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6732673267326733</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>120</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F12" t="n">
+        <v>29</v>
+      </c>
+      <c r="G12" t="n">
+        <v>116</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7117903930131004</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7032844164919636</v>
+      </c>
+      <c r="D13" t="n">
+        <v>68</v>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G13" t="n">
+        <v>95</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6732673267326733</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
+++ b/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,396 @@
         <v>0.6732673267326733</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>120</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n">
+        <v>34</v>
+      </c>
+      <c r="F15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>116</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.6986899563318777</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7125786163522012</v>
+      </c>
+      <c r="D16" t="n">
+        <v>57</v>
+      </c>
+      <c r="E16" t="n">
+        <v>47</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22</v>
+      </c>
+      <c r="G16" t="n">
+        <v>103</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6229508196721312</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D17" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>34</v>
+      </c>
+      <c r="F18" t="n">
+        <v>29</v>
+      </c>
+      <c r="G18" t="n">
+        <v>116</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.6986899563318777</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7125786163522012</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57</v>
+      </c>
+      <c r="E19" t="n">
+        <v>47</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22</v>
+      </c>
+      <c r="G19" t="n">
+        <v>103</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6229508196721312</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D20" t="n">
+        <v>46</v>
+      </c>
+      <c r="E20" t="n">
+        <v>30</v>
+      </c>
+      <c r="F20" t="n">
+        <v>35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>120</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" t="n">
+        <v>34</v>
+      </c>
+      <c r="F21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G21" t="n">
+        <v>116</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.6986899563318777</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7125786163522012</v>
+      </c>
+      <c r="D22" t="n">
+        <v>57</v>
+      </c>
+      <c r="E22" t="n">
+        <v>47</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>103</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6229508196721312</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D23" t="n">
+        <v>46</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>120</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29</v>
+      </c>
+      <c r="G24" t="n">
+        <v>116</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.6681222707423581</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7032145352900069</v>
+      </c>
+      <c r="D25" t="n">
+        <v>47</v>
+      </c>
+      <c r="E25" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>106</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5529411764705883</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7186147186147186</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7263801537386443</v>
+      </c>
+      <c r="D26" t="n">
+        <v>46</v>
+      </c>
+      <c r="E26" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" t="n">
+        <v>120</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5859872611464968</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.7248908296943232</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6802935010482181</v>
+      </c>
+      <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="n">
+        <v>34</v>
+      </c>
+      <c r="F27" t="n">
+        <v>29</v>
+      </c>
+      <c r="G27" t="n">
+        <v>116</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6134969325153374</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.7117903930131004</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7032844164919636</v>
+      </c>
+      <c r="D28" t="n">
+        <v>68</v>
+      </c>
+      <c r="E28" t="n">
+        <v>55</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>95</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6732673267326733</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
+++ b/eda/ket_qua/ket_qua_modeldecisiontree.xlsx
@@ -1,37 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ai-project\eda\ket_qua\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6D2A3D-6C99-4FC3-BC83-EF2ACBCE4035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Validation Accuracy</t>
+  </si>
+  <si>
+    <t>Test Accuracy</t>
+  </si>
+  <si>
+    <t>Mean KFold Accuracy</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>F1-score</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +81,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,210 +405,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Validation Accuracy</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Test Accuracy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mean KFold Accuracy</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FN</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>F1-score</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>0.7186147186147186</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.7263801537386443</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>0.72638015373864429</v>
+      </c>
+      <c r="D2">
         <v>46</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>30</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>35</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>120</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.5859872611464968</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.7229437229437229</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.713277428371768</v>
-      </c>
-      <c r="D3" t="n">
-        <v>47</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="B3">
+        <v>0.72489082969432317</v>
+      </c>
+      <c r="C3">
+        <v>0.68029350104821806</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
         <v>34</v>
       </c>
-      <c r="G3" t="n">
-        <v>120</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5949367088607594</v>
+      <c r="F3">
+        <v>29</v>
+      </c>
+      <c r="G3">
+        <v>116</v>
+      </c>
+      <c r="H3">
+        <v>0.61349693251533743</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.8271604938271605</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7705627705627706</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6964709993011879</v>
-      </c>
-      <c r="D4" t="n">
-        <v>63</v>
-      </c>
-      <c r="E4" t="n">
-        <v>35</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" t="n">
-        <v>115</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7039106145251397</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.7186147186147186</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.7263801537386443</v>
-      </c>
-      <c r="D5" t="n">
-        <v>46</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" t="n">
-        <v>35</v>
-      </c>
-      <c r="G5" t="n">
-        <v>120</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.5859872611464968</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.7248908296943232</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6802935010482181</v>
-      </c>
-      <c r="D6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" t="n">
-        <v>34</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G6" t="n">
-        <v>116</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6134969325153374</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>0.8125</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.7117903930131004</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B4">
+        <v>0.71179039301310043</v>
+      </c>
+      <c r="C4">
         <v>0.7032844164919636</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D4">
         <v>68</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E4">
         <v>55</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F4">
         <v>11</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G4">
         <v>95</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.6732673267326733</v>
+      <c r="H4">
+        <v>0.67326732673267331</v>
       </c>
     </row>
   </sheetData>
